--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488083_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488083_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.083</v>
+        <v>6.0297</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3141</v>
+        <v>5.9066</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7689</v>
+        <v>0.1231</v>
       </c>
       <c r="G2" t="n">
         <v>7.1136</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9626</v>
+        <v>0.9093</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.2644</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2907</v>
+        <v>0.6449</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4074</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3538</v>
+        <v>5.0586</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9662</v>
+        <v>6.5588</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6124</v>
+        <v>-1.5001</v>
       </c>
       <c r="G3" t="n">
         <v>5.2827</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9412</v>
+        <v>0.646</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6095</v>
+        <v>0.202</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3317</v>
+        <v>0.444</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4478</v>
+        <v>3.5673</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4113</v>
+        <v>3.615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0365</v>
+        <v>-0.0477</v>
       </c>
       <c r="G4" t="n">
         <v>2.7038</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.744</v>
+        <v>0.8635</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0552</v>
+        <v>0.2589</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6888</v>
+        <v>0.6046</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4087</v>
+        <v>3.0685</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2145</v>
+        <v>4.5201</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-1.4517</v>
       </c>
       <c r="G5" t="n">
         <v>1.9266</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3365</v>
+        <v>-0.0037</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8736</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2101</v>
+        <v>0.5642</v>
       </c>
       <c r="V5" t="n">
         <v>1.7403</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. PERERIRA</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.507</v>
+        <v>0.6448</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2628</v>
+        <v>1.3435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7698</v>
+        <v>-0.6987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7056</v>
+        <v>-0.7315</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1113</v>
+        <v>-3.1191</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4057</v>
+        <v>2.3876</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4257</v>
+        <v>1.0613</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3052</v>
+        <v>-0.9074</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>1.9687</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7201</v>
+        <v>-1.7928</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1939</v>
+        <v>-2.2117</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5262</v>
+        <v>0.4189</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3168</v>
+        <v>-0.4056</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4919</v>
+        <v>-0.3192</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1752</v>
+        <v>-0.0864</v>
       </c>
       <c r="V6" t="n">
-        <v>0.674</v>
+        <v>0.1962</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X6" t="n">
-        <v>0.674</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>T. PERERIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4764</v>
+        <v>0.3875</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3435</v>
+        <v>-0.4665</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8672</v>
+        <v>0.854</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7315</v>
+        <v>0.7056</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1191</v>
+        <v>1.1113</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3876</v>
+        <v>-0.4057</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0613</v>
+        <v>1.4257</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9074</v>
+        <v>1.3052</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9687</v>
+        <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7928</v>
+        <v>-0.7201</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2117</v>
+        <v>-0.1939</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4189</v>
+        <v>-0.5262</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5858</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R7" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.1973</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3192</v>
+        <v>0.2882</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2548</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1962</v>
+        <v>0.674</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7366</v>
+        <v>-0.2416</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6247</v>
+        <v>0.7266</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3613</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>1.5344</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1145</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8736</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2409</v>
+        <v>0.1522</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1476</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9428</v>
+        <v>-0.7463</v>
       </c>
       <c r="E9" t="n">
         <v>-1.3814</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4386</v>
+        <v>0.6351</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3676</v>
@@ -1156,13 +1156,13 @@
         <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3681</v>
+        <v>-0.1716</v>
       </c>
       <c r="T9" t="n">
         <v>-0.132</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2361</v>
+        <v>-0.0396</v>
       </c>
       <c r="V9" t="n">
         <v>0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0483</v>
+        <v>-0.8518</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3409</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7074</v>
+        <v>-0.5109</v>
       </c>
       <c r="G10" t="n">
         <v>0.5474</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8821</v>
+        <v>-0.6856</v>
       </c>
       <c r="T10" t="n">
         <v>-0.6864</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1958</v>
+        <v>0.0008</v>
       </c>
       <c r="V10" t="n">
         <v>0.674</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5211</v>
+        <v>-1.4088</v>
       </c>
       <c r="E11" t="n">
         <v>0.08210000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6031</v>
+        <v>-1.4908</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0255</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6849</v>
+        <v>-0.5726</v>
       </c>
       <c r="T11" t="n">
         <v>-0.624</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0609</v>
+        <v>0.0514</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2071</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5309</v>
+        <v>-2.0673</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.608</v>
+        <v>-0.2006</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9229</v>
+        <v>-1.8667</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2564</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.671</v>
+        <v>-0.2074</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4368</v>
+        <v>-0.0293</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6288</v>
+        <v>-2.5726</v>
       </c>
       <c r="E13" t="n">
         <v>-0.7877999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8409</v>
+        <v>-1.7848</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9379</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4838</v>
+        <v>-0.4276</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.8682</v>
+        <v>10.868</v>
       </c>
       <c r="E14" t="n">
         <v>19.5755</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.7073</v>
+        <v>-8.7074</v>
       </c>
       <c r="G14" t="n">
         <v>15.4952</v>
@@ -1546,13 +1546,13 @@
         <v>13.8757</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4774000000000002</v>
+        <v>-0.4775000000000003</v>
       </c>
       <c r="T14" t="n">
         <v>-2.3667</v>
       </c>
       <c r="U14" t="n">
-        <v>1.889199999999999</v>
+        <v>1.889</v>
       </c>
       <c r="V14" t="n">
         <v>-3.1583</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3827</v>
+        <v>3.1228</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2034</v>
+        <v>3.9996</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8207</v>
+        <v>-0.8769</v>
       </c>
       <c r="G15" t="n">
         <v>1.4804</v>
@@ -1624,13 +1624,13 @@
         <v>0.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.4442</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1176</v>
+        <v>-0.0862</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5865</v>
+        <v>0.5304</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4059</v>
+        <v>1.236</v>
       </c>
       <c r="E17" t="n">
-        <v>2.525</v>
+        <v>5.9729</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1191</v>
+        <v>-4.737</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5333</v>
+        <v>-0.6015</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3957</v>
+        <v>-2.7924</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1376</v>
+        <v>2.1909</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3854</v>
+        <v>5.7499</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2648</v>
+        <v>1.0296</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1205</v>
+        <v>4.7202</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.852</v>
+        <v>-6.3514</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8691</v>
+        <v>-3.822</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0171</v>
+        <v>-2.5294</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>-2.3787</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4437</v>
+        <v>-0.6864</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7343</v>
+        <v>-0.6826</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7094</v>
+        <v>-0.0038</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.364</v>
+        <v>2.5239</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036</v>
+        <v>3.2843</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.9676</v>
+        <v>-0.7605</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3087</v>
+        <v>0.5981</v>
       </c>
       <c r="E18" t="n">
-        <v>5.158</v>
+        <v>1.9138</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8493</v>
+        <v>-1.3156</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6015</v>
+        <v>0.5333</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7924</v>
+        <v>0.3957</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1909</v>
+        <v>0.1376</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7499</v>
+        <v>1.3854</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0296</v>
+        <v>1.2648</v>
       </c>
       <c r="L18" t="n">
-        <v>4.7202</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.3514</v>
+        <v>-0.852</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.822</v>
+        <v>-0.8691</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5294</v>
+        <v>0.0171</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3787</v>
+        <v>-0.1982</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6136</v>
+        <v>0.636</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4975</v>
+        <v>0.1231</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1161</v>
+        <v>0.5129</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5239</v>
+        <v>-1.364</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2843</v>
+        <v>0.6036</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7605</v>
+        <v>-1.9676</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.211</v>
+        <v>0.1453</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4499</v>
+        <v>0.966</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2389</v>
+        <v>-0.8207</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0658</v>
+        <v>1.164</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3834</v>
+        <v>1.6959</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3175</v>
+        <v>-0.5319</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0604</v>
+        <v>3.0773</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0202</v>
+        <v>3.632</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>-0.5547</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1262</v>
+        <v>-1.9133</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4036</v>
+        <v>-1.9361</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2774</v>
+        <v>0.0228</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1982</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>-3.1716</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3197</v>
+        <v>-0.0073</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.312</v>
+        <v>0.1901</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6317</v>
+        <v>-0.1974</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2666</v>
+        <v>0.3762</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>-0.4939</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7104</v>
+        <v>-0.3618</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2779</v>
+        <v>-0.348</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5675</v>
+        <v>-0.0138</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0931</v>
+        <v>-0.0658</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4508</v>
+        <v>-0.3834</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3577</v>
+        <v>0.3175</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1611</v>
+        <v>0.0604</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0804</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2542</v>
+        <v>-0.1262</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5315</v>
+        <v>-0.4036</v>
       </c>
       <c r="O20" t="n">
         <v>0.2774</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1688</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2496</v>
+        <v>-0.2101</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3336</v>
+        <v>0.379</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1066</v>
+        <v>-0.2666</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1066</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8976</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4566</v>
+        <v>-1.176</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3542</v>
+        <v>0.5394</v>
       </c>
       <c r="G21" t="n">
-        <v>1.164</v>
+        <v>-0.0931</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6959</v>
+        <v>-0.4508</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5319</v>
+        <v>0.3577</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0773</v>
+        <v>0.1611</v>
       </c>
       <c r="K21" t="n">
-        <v>3.632</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5547</v>
+        <v>0.0804</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9133</v>
+        <v>-0.2542</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9361</v>
+        <v>-0.5315</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0228</v>
+        <v>0.2774</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3876</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1716</v>
+        <v>-1.1893</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0502</v>
+        <v>0.1578</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3192</v>
+        <v>-0.1477</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7309</v>
+        <v>0.3055</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3762</v>
+        <v>-0.1066</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4939</v>
+        <v>-0.1066</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MATEOS PENA</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2056</v>
+        <v>-1.1522</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1861</v>
+        <v>1.0589</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9805</v>
+        <v>-2.2111</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2702</v>
+        <v>-2.3295</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6403</v>
+        <v>-0.5827</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6299</v>
+        <v>-1.7468</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6156</v>
+        <v>2.219</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5782</v>
+        <v>2.0985</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0374</v>
+        <v>0.1205</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3455</v>
+        <v>-4.5486</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.062</v>
+        <v>-2.6812</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4075</v>
+        <v>-1.8674</v>
       </c>
       <c r="P22" t="n">
         <v>0.5947</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4699</v>
+        <v>-0.3578</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4295</v>
+        <v>-0.5743</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0403</v>
+        <v>0.2165</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>A. MATEOS PENA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7634</v>
+        <v>-1.5112</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4477</v>
+        <v>-2.4917</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2111</v>
+        <v>0.9805</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3295</v>
+        <v>-2.2702</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5827</v>
+        <v>-0.6403</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7468</v>
+        <v>-1.6299</v>
       </c>
       <c r="J23" t="n">
-        <v>2.219</v>
+        <v>-2.6156</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0985</v>
+        <v>-0.5782</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1205</v>
+        <v>-2.0374</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.5486</v>
+        <v>0.3455</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.6812</v>
+        <v>-0.062</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8674</v>
+        <v>0.4075</v>
       </c>
       <c r="P23" t="n">
         <v>0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9691</v>
+        <v>0.1643</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1855</v>
+        <v>0.1239</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2165</v>
+        <v>0.0403</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8793</v>
+        <v>-3.578</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4388</v>
+        <v>-0.7444</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4405</v>
+        <v>-2.8336</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8148</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>0.707</v>
+        <v>0.0083</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3599</v>
+        <v>0.0543</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3471</v>
+        <v>-0.046</v>
       </c>
       <c r="V24" t="n">
         <v>0.0392</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3604</v>
+        <v>-4.1192</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2466</v>
+        <v>-1.0616</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1138</v>
+        <v>-3.0576</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4759</v>
@@ -2404,13 +2404,13 @@
         <v>1.9822</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.0129</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7894</v>
+        <v>-0.0255</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0177</v>
+        <v>0.0384</v>
       </c>
       <c r="V25" t="n">
         <v>0.5331</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4484</v>
+        <v>-6.1219</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9947</v>
+        <v>-0.8928</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.4537</v>
+        <v>-5.2291</v>
       </c>
       <c r="G26" t="n">
         <v>-6.5326</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3898</v>
+        <v>-0.0633</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.756</v>
+        <v>-0.6541</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3662</v>
+        <v>0.5909</v>
       </c>
       <c r="V26" t="n">
         <v>-0.1207</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.8681</v>
+        <v>-10.868</v>
       </c>
       <c r="E27" t="n">
-        <v>8.707399999999998</v>
+        <v>8.7074</v>
       </c>
       <c r="F27" t="n">
         <v>-19.5755</v>
@@ -2560,13 +2560,13 @@
         <v>14.8668</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4774000000000001</v>
+        <v>0.4774999999999999</v>
       </c>
       <c r="T27" t="n">
         <v>-1.8891</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3666</v>
+        <v>2.3667</v>
       </c>
       <c r="V27" t="n">
         <v>3.1586</v>
